--- a/api/templates/device_utilization_per_day/uk.xlsx
+++ b/api/templates/device_utilization_per_day/uk.xlsx
@@ -1,38 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\device_utilization_per_day\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A5F0A8-C238-41E3-94F6-8588E4CF37BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Використання приладу за добу" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Використання приладу за добу" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Використання приладу за добу, кількість тестів та відсоток</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
+  </si>
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Пристрій</t>
+  </si>
+  <si>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>Загальні результати в період</t>
+  </si>
+  <si>
+    <t>Щоденна ємність пристрою</t>
+  </si>
+  <si>
+    <t>Коефіцієнт використання (за винятком вихідних)</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;totalResults&gt;</t>
   </si>
   <si>
@@ -40,61 +62,41 @@
   </si>
   <si>
     <t>&lt;utilizationRate&gt;</t>
-  </si>
-  <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Використання приладу за добу, кількість тестів та відсоток</t>
-  </si>
-  <si>
-    <t>Пристрій</t>
-  </si>
-  <si>
-    <t>Загальні результати в період</t>
-  </si>
-  <si>
-    <t>Щоденна ємність пристрою</t>
-  </si>
-  <si>
-    <t>Коефіцієнт використання (за винятком вихідних)</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
-      <charset val="1"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -120,40 +122,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left style="medium"/>
       <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -163,7 +149,6 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -171,80 +156,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -552,77 +470,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.796875" customWidth="1"/>
-    <col min="2" max="2" width="20.19921875" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="28.296875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="20.19921875" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="28.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="31.8" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization_per_day/uk.xlsx
+++ b/api/templates/device_utilization_per_day/uk.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BCDD34-BA02-1C4A-9984-491F5AB49133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Використання приладу за добу" state="visible" r:id="rId4"/>
+    <sheet name="Використання приладу за добу" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -67,36 +68,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -113,7 +114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -122,24 +123,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -149,14 +157,12 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,85 +476,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.796875" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="28.296875" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="31.8" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:5" ht="31.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization_per_day/uk.xlsx
+++ b/api/templates/device_utilization_per_day/uk.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BCDD34-BA02-1C4A-9984-491F5AB49133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13180"/>
   </bookViews>
   <sheets>
-    <sheet name="Використання приладу за добу" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Використання приладу за добу" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Використання приладу за добу, кількість тестів та відсоток</t>
   </si>
@@ -32,15 +31,18 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Сайт</t>
+  </si>
+  <si>
     <t>Пристрій</t>
   </si>
   <si>
-    <t>Сайт</t>
-  </si>
-  <si>
     <t>Загальні результати в період</t>
   </si>
   <si>
@@ -50,10 +52,10 @@
     <t>Коефіцієнт використання (за винятком вихідних)</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;totalResults&gt;</t>
@@ -68,36 +70,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -123,31 +125,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -157,12 +145,12 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,9 +464,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -487,74 +475,79 @@
     <col min="5" max="5" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="16.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="31.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="31.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
+      <c r="E9" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization_per_day/uk.xlsx
+++ b/api/templates/device_utilization_per_day/uk.xlsx
@@ -142,9 +142,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -501,7 +502,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -511,36 +512,36 @@
       </c>
     </row>
     <row r="8" ht="31.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/api/templates/device_utilization_per_day/uk.xlsx
+++ b/api/templates/device_utilization_per_day/uk.xlsx
@@ -31,7 +31,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -142,10 +142,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -502,7 +501,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -512,36 +511,36 @@
       </c>
     </row>
     <row r="8" ht="31.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>16</v>
       </c>
     </row>
